--- a/DataAnalysis/CJ/0.2/Results.xlsx
+++ b/DataAnalysis/CJ/0.2/Results.xlsx
@@ -1,25 +1,119 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CJ\0.2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E5F9CD-E5FF-4870-9FAB-2342D67CF086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="NOAUG" sheetId="2" r:id="rId2"/>
+    <sheet name="ADV_CLSDIV" sheetId="3" r:id="rId3"/>
+    <sheet name="ADV_NOCLSDIV" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="23">
+  <si>
+    <t>ERR_0_i</t>
+  </si>
+  <si>
+    <t>ERR_1_i</t>
+  </si>
+  <si>
+    <t>ERR_2_i</t>
+  </si>
+  <si>
+    <t>ERR_i</t>
+  </si>
+  <si>
+    <t>MINERR_i</t>
+  </si>
+  <si>
+    <t>CIC</t>
+  </si>
+  <si>
+    <t>ERR_0</t>
+  </si>
+  <si>
+    <t>ERR_0STD</t>
+  </si>
+  <si>
+    <t>ERR_1</t>
+  </si>
+  <si>
+    <t>ERR_1STD</t>
+  </si>
+  <si>
+    <t>ERR_2</t>
+  </si>
+  <si>
+    <t>ERR_2STD</t>
+  </si>
+  <si>
+    <t>ERR</t>
+  </si>
+  <si>
+    <t>ERRSTD</t>
+  </si>
+  <si>
+    <t>CICSTD</t>
+  </si>
+  <si>
+    <t>NOAUG</t>
+  </si>
+  <si>
+    <t>ADV_CLSDIV</t>
+  </si>
+  <si>
+    <t>ADV_NOCLSDIV</t>
+  </si>
+  <si>
+    <t>eps=0.1</t>
+  </si>
+  <si>
+    <t>eps=0.0056</t>
+  </si>
+  <si>
+    <t>eps=0.0003</t>
+  </si>
+  <si>
+    <t>eps=1.778e-5</t>
+  </si>
+  <si>
+    <t>eps=e-6</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -53,7 +147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +424,3380 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0070ADD-01EC-4620-990C-69699D9624BD}">
+  <dimension ref="Q1:AG33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q2" t="e">
+        <f>AVERAGE(C2,D2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R2" t="e">
+        <f>AVERAGE(H2,I2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S2" t="e">
+        <f>AVERAGE(M2,N2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T2" t="e">
+        <f>AVERAGE(Q2:S2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U2" t="e">
+        <f>MIN(Q2:S2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V2" t="e">
+        <f>(1/3)*(T2-U2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X2" t="e">
+        <f>AVERAGE(Q2:Q33)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y2" t="e">
+        <f>_xlfn.STDEV.S(Q2:Q33)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z2" t="e">
+        <f>AVERAGE(R2:R33)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA2" t="e">
+        <f>_xlfn.STDEV.S(R2:R33)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB2" t="e">
+        <f>AVERAGE(S2:S33)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC2" t="e">
+        <f>_xlfn.STDEV.S(S2:S33)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD2" t="e">
+        <f>AVERAGE(T2:T33)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE2" t="e">
+        <f>_xlfn.STDEV.S(T2:T33)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF2" t="e">
+        <f>AVERAGE(V2:V33)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG2" t="e">
+        <f>_xlfn.STDEV.S(V2:V33)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="3" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q3" t="e">
+        <f t="shared" ref="Q3:Q33" si="0">AVERAGE(C3,D3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R3" t="e">
+        <f t="shared" ref="R3:R33" si="1">AVERAGE(H3,I3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S3" t="e">
+        <f t="shared" ref="S3:S33" si="2">AVERAGE(M3,N3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T3" t="e">
+        <f t="shared" ref="T3:T33" si="3">AVERAGE(Q3:S3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U3" t="e">
+        <f t="shared" ref="U3:U33" si="4">MIN(Q3:S3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V3" t="e">
+        <f t="shared" ref="V3:V33" si="5">(1/3)*(T3-U3)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q4" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R4" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S4" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T4" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U4" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V4" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q5" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R5" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S5" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T5" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U5" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V5" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q6" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R6" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S6" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T6" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U6" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V6" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q7" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U7" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V7" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R8" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S8" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T8" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U8" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V8" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q9" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S9" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T9" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U9" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V9" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q10" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S10" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T10" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U10" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V10" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R11" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S11" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T11" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V11" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q12" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R12" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S12" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T12" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U12" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V12" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q13" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R13" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S13" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T13" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U13" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V13" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q14" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R14" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T14" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U14" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V14" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R15" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S15" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V15" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="17:33" x14ac:dyDescent="0.3">
+      <c r="Q16" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R16" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T16" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U16" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q17" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R17" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T17" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U17" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q18" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R18" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S18" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T18" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V18" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q19" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R19" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S19" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U19" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V19" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R20" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S20" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T20" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U20" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V20" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q21" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R21" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S21" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T21" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U21" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V21" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q22" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R22" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S22" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T22" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U22" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V22" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q23" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R23" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S23" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T23" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U23" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V23" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q24" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R24" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S24" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T24" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U24" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V24" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R25" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S25" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T25" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U25" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V25" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q26" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R26" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S26" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T26" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U26" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V26" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q27" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R27" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S27" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T27" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U27" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V27" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q28" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R28" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T28" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U28" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V28" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q29" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R29" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S29" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T29" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U29" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V29" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q30" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R30" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S30" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T30" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U30" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V30" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q31" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R31" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S31" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T31" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U31" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V31" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q32" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R32" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S32" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T32" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U32" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V32" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="33" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="Q33" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R33" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S33" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T33" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U33" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V33" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F61CE5A4-107E-4BE1-BA89-5E6F058EC1FC}">
+  <dimension ref="A1:AG45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q3" t="e">
+        <f>AVERAGE(C3,D3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R3" t="e">
+        <f>AVERAGE(H3,I3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S3" t="e">
+        <f>AVERAGE(M3,N3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T3" t="e">
+        <f>AVERAGE(Q3:S3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U3" t="e">
+        <f>MIN(Q3:S3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V3" t="e">
+        <f>(1/3)*(T3-U3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X3" t="e">
+        <f>AVERAGE(Q3:Q9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y3" t="e">
+        <f>_xlfn.STDEV.S(Q3:Q9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z3" t="e">
+        <f>AVERAGE(R3:R9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA3" t="e">
+        <f>_xlfn.STDEV.S(R3:R9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB3" t="e">
+        <f>AVERAGE(S3:S9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC3" t="e">
+        <f>_xlfn.STDEV.S(S3:S9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD3" t="e">
+        <f>AVERAGE(T3:T9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE3" t="e">
+        <f>_xlfn.STDEV.S(T3:T9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF3" t="e">
+        <f>AVERAGE(V3:V9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG3" t="e">
+        <f>_xlfn.STDEV.S(V3:V9)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q4" t="e">
+        <f t="shared" ref="Q4:Q45" si="0">AVERAGE(C4,D4)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R4" t="e">
+        <f t="shared" ref="R4:R45" si="1">AVERAGE(H4,I4)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S4" t="e">
+        <f t="shared" ref="S4:S45" si="2">AVERAGE(M4,N4)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T4" t="e">
+        <f t="shared" ref="T4:T45" si="3">AVERAGE(Q4:S4)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U4" t="e">
+        <f t="shared" ref="U4:U45" si="4">MIN(Q4:S4)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V4" t="e">
+        <f t="shared" ref="V4:V45" si="5">(1/3)*(T4-U4)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q5" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R5" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S5" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T5" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U5" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V5" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q6" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R6" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S6" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T6" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U6" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V6" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q7" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U7" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V7" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R8" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S8" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T8" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U8" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V8" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q9" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S9" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T9" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U9" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V9" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q12" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R12" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S12" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T12" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U12" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V12" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X12" t="e">
+        <f>AVERAGE(Q12:Q18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y12" t="e">
+        <f>_xlfn.STDEV.S(Q12:Q18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z12" t="e">
+        <f>AVERAGE(R12:R18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA12" t="e">
+        <f>_xlfn.STDEV.S(R12:R18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB12" t="e">
+        <f>AVERAGE(S12:S18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC12" t="e">
+        <f>_xlfn.STDEV.S(S12:S18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD12" t="e">
+        <f>AVERAGE(T12:T18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE12" t="e">
+        <f>_xlfn.STDEV.S(T12:T18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF12" t="e">
+        <f>AVERAGE(V12:V18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG12" t="e">
+        <f>_xlfn.STDEV.S(V12:V18)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q13" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R13" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S13" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T13" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U13" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V13" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q14" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R14" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T14" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U14" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V14" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R15" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S15" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V15" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q16" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R16" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T16" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U16" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q17" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R17" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T17" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U17" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q18" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R18" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S18" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T18" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V18" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q21" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R21" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S21" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T21" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U21" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V21" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X21" t="e">
+        <f>AVERAGE(Q21:Q27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y21" t="e">
+        <f>_xlfn.STDEV.S(Q21:Q27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z21" t="e">
+        <f>AVERAGE(R21:R27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA21" t="e">
+        <f>_xlfn.STDEV.S(R21:R27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB21" t="e">
+        <f>AVERAGE(S21:S27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC21" t="e">
+        <f>_xlfn.STDEV.S(S21:S27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD21" t="e">
+        <f>AVERAGE(T21:T27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE21" t="e">
+        <f>_xlfn.STDEV.S(T21:T27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF21" t="e">
+        <f>AVERAGE(V21:V27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG21" t="e">
+        <f>_xlfn.STDEV.S(V21:V27)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q22" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R22" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S22" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T22" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U22" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V22" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q23" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R23" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S23" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T23" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U23" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V23" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q24" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R24" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S24" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T24" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U24" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V24" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R25" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S25" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T25" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U25" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V25" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q26" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R26" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S26" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T26" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U26" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V26" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q27" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R27" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S27" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T27" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U27" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V27" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q30" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R30" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S30" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T30" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U30" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V30" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X30" t="e">
+        <f>AVERAGE(Q30:Q36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y30" t="e">
+        <f>_xlfn.STDEV.S(Q30:Q36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z30" t="e">
+        <f>AVERAGE(R30:R36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA30" t="e">
+        <f>_xlfn.STDEV.S(R30:R36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB30" t="e">
+        <f>AVERAGE(S30:S36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC30" t="e">
+        <f>_xlfn.STDEV.S(S30:S36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD30" t="e">
+        <f>AVERAGE(T30:T36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE30" t="e">
+        <f>_xlfn.STDEV.S(T30:T36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF30" t="e">
+        <f>AVERAGE(V30:V36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG30" t="e">
+        <f>_xlfn.STDEV.S(V30:V36)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q31" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R31" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S31" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T31" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U31" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V31" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q32" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R32" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S32" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T32" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U32" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V32" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q33" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R33" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S33" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T33" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U33" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V33" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q34" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R34" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S34" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T34" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U34" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V34" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q35" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R35" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S35" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T35" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U35" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V35" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q36" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R36" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S36" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T36" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U36" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V36" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q39" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R39" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S39" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T39" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U39" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V39" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X39" t="e">
+        <f>AVERAGE(Q39:Q45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y39" t="e">
+        <f>_xlfn.STDEV.S(Q39:Q45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z39" t="e">
+        <f>AVERAGE(R39:R45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA39" t="e">
+        <f>_xlfn.STDEV.S(R39:R45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB39" t="e">
+        <f>AVERAGE(S39:S45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC39" t="e">
+        <f>_xlfn.STDEV.S(S39:S45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD39" t="e">
+        <f>AVERAGE(T39:T45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE39" t="e">
+        <f>_xlfn.STDEV.S(T39:T45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF39" t="e">
+        <f>AVERAGE(V39:V45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG39" t="e">
+        <f>_xlfn.STDEV.S(V39:V45)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q40" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R40" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S40" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T40" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U40" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V40" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q41" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R41" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S41" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T41" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U41" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V41" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q42" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R42" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S42" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T42" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U42" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V42" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q43" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R43" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S43" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T43" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U43" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V43" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q44" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R44" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S44" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T44" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V44" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q45" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R45" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S45" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T45" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U45" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V45" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BEE07E7-E9F2-4A3E-A357-F6ABAE306089}">
+  <dimension ref="A1:AG45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q3" t="e">
+        <f>AVERAGE(C3,D3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R3" t="e">
+        <f>AVERAGE(H3,I3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S3" t="e">
+        <f>AVERAGE(M3,N3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T3" t="e">
+        <f>AVERAGE(Q3:S3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U3" t="e">
+        <f>MIN(Q3:S3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V3" t="e">
+        <f>(1/3)*(T3-U3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X3" t="e">
+        <f>AVERAGE(Q3:Q9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y3" t="e">
+        <f>_xlfn.STDEV.S(Q3:Q9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z3" t="e">
+        <f>AVERAGE(R3:R9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA3" t="e">
+        <f>_xlfn.STDEV.S(R3:R9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB3" t="e">
+        <f>AVERAGE(S3:S9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC3" t="e">
+        <f>_xlfn.STDEV.S(S3:S9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD3" t="e">
+        <f>AVERAGE(T3:T9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE3" t="e">
+        <f>_xlfn.STDEV.S(T3:T9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF3" t="e">
+        <f>AVERAGE(V3:V9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG3" t="e">
+        <f>_xlfn.STDEV.S(V3:V9)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q4" t="e">
+        <f t="shared" ref="Q4:Q45" si="0">AVERAGE(C4,D4)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R4" t="e">
+        <f t="shared" ref="R4:R45" si="1">AVERAGE(H4,I4)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S4" t="e">
+        <f t="shared" ref="S4:S45" si="2">AVERAGE(M4,N4)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T4" t="e">
+        <f t="shared" ref="T4:T45" si="3">AVERAGE(Q4:S4)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U4" t="e">
+        <f t="shared" ref="U4:U45" si="4">MIN(Q4:S4)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V4" t="e">
+        <f t="shared" ref="V4:V45" si="5">(1/3)*(T4-U4)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q5" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R5" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S5" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T5" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U5" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V5" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q6" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R6" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S6" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T6" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U6" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V6" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q7" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U7" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V7" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R8" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S8" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T8" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U8" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V8" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q9" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S9" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T9" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U9" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V9" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q12" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R12" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S12" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T12" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U12" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V12" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X12" t="e">
+        <f>AVERAGE(Q12:Q18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y12" t="e">
+        <f>_xlfn.STDEV.S(Q12:Q18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z12" t="e">
+        <f>AVERAGE(R12:R18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA12" t="e">
+        <f>_xlfn.STDEV.S(R12:R18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB12" t="e">
+        <f>AVERAGE(S12:S18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC12" t="e">
+        <f>_xlfn.STDEV.S(S12:S18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD12" t="e">
+        <f>AVERAGE(T12:T18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE12" t="e">
+        <f>_xlfn.STDEV.S(T12:T18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF12" t="e">
+        <f>AVERAGE(V12:V18)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG12" t="e">
+        <f>_xlfn.STDEV.S(V12:V18)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q13" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R13" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S13" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T13" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U13" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V13" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q14" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R14" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T14" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U14" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V14" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R15" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S15" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V15" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q16" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R16" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T16" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U16" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q17" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R17" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T17" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U17" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q18" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R18" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S18" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T18" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V18" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q21" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R21" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S21" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T21" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U21" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V21" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X21" t="e">
+        <f>AVERAGE(Q21:Q27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y21" t="e">
+        <f>_xlfn.STDEV.S(Q21:Q27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z21" t="e">
+        <f>AVERAGE(R21:R27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA21" t="e">
+        <f>_xlfn.STDEV.S(R21:R27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB21" t="e">
+        <f>AVERAGE(S21:S27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC21" t="e">
+        <f>_xlfn.STDEV.S(S21:S27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD21" t="e">
+        <f>AVERAGE(T21:T27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE21" t="e">
+        <f>_xlfn.STDEV.S(T21:T27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF21" t="e">
+        <f>AVERAGE(V21:V27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG21" t="e">
+        <f>_xlfn.STDEV.S(V21:V27)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q22" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R22" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S22" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T22" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U22" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V22" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q23" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R23" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S23" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T23" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U23" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V23" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q24" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R24" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S24" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T24" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U24" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V24" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R25" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S25" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T25" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U25" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V25" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q26" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R26" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S26" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T26" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U26" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V26" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q27" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R27" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S27" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T27" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U27" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V27" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q30" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R30" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S30" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T30" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U30" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V30" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X30" t="e">
+        <f>AVERAGE(Q30:Q36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y30" t="e">
+        <f>_xlfn.STDEV.S(Q30:Q36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z30" t="e">
+        <f>AVERAGE(R30:R36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA30" t="e">
+        <f>_xlfn.STDEV.S(R30:R36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB30" t="e">
+        <f>AVERAGE(S30:S36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC30" t="e">
+        <f>_xlfn.STDEV.S(S30:S36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD30" t="e">
+        <f>AVERAGE(T30:T36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE30" t="e">
+        <f>_xlfn.STDEV.S(T30:T36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF30" t="e">
+        <f>AVERAGE(V30:V36)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG30" t="e">
+        <f>_xlfn.STDEV.S(V30:V36)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q31" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R31" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S31" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T31" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U31" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V31" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q32" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R32" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S32" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T32" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U32" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V32" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q33" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R33" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S33" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T33" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U33" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V33" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q34" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R34" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S34" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T34" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U34" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V34" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q35" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R35" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S35" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T35" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U35" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V35" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q36" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R36" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S36" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T36" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U36" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V36" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q39" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R39" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S39" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T39" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U39" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V39" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X39" t="e">
+        <f>AVERAGE(Q39:Q45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y39" t="e">
+        <f>_xlfn.STDEV.S(Q39:Q45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z39" t="e">
+        <f>AVERAGE(R39:R45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA39" t="e">
+        <f>_xlfn.STDEV.S(R39:R45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB39" t="e">
+        <f>AVERAGE(S39:S45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC39" t="e">
+        <f>_xlfn.STDEV.S(S39:S45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD39" t="e">
+        <f>AVERAGE(T39:T45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE39" t="e">
+        <f>_xlfn.STDEV.S(T39:T45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF39" t="e">
+        <f>AVERAGE(V39:V45)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG39" t="e">
+        <f>_xlfn.STDEV.S(V39:V45)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q40" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R40" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S40" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T40" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U40" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V40" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q41" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R41" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S41" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T41" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U41" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V41" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q42" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R42" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S42" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T42" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U42" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V42" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q43" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R43" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S43" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T43" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U43" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V43" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q44" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R44" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S44" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T44" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V44" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="Q45" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R45" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S45" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T45" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U45" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V45" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DataAnalysis/CJ/0.2/Results.xlsx
+++ b/DataAnalysis/CJ/0.2/Results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CI\0.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CJ\0.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B691CEA8-B79E-422C-872E-9BF628567C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136CEC64-E386-448A-AC3D-5D8FB9C3CFA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="24">
   <si>
     <t>ERR_i_0</t>
   </si>
@@ -106,21 +106,19 @@
   <si>
     <t>ADV_NOCLSDIV</t>
   </si>
+  <si>
+    <t>ep=0.1</t>
+  </si>
+  <si>
+    <t>ep=0.0001</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -148,9 +146,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -431,85 +428,151 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:T4"/>
+  <dimension ref="B1:N4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
       <c r="K1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="E2">
+        <v>21.65</v>
+      </c>
+      <c r="F2">
+        <v>1.8112303982529543</v>
+      </c>
+      <c r="G2">
+        <v>12.75</v>
+      </c>
+      <c r="H2">
+        <v>2.3003622903070435</v>
+      </c>
+      <c r="I2">
+        <v>31.05</v>
+      </c>
+      <c r="J2">
+        <v>2.4318488622628025</v>
+      </c>
+      <c r="K2">
+        <v>21.81666666666667</v>
+      </c>
+      <c r="L2">
+        <v>0.86584719092036688</v>
+      </c>
+      <c r="M2">
+        <v>9.0666666666666664</v>
+      </c>
+      <c r="N2">
+        <v>1.6872799353536168</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-    </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3">
+        <v>22.7</v>
+      </c>
+      <c r="F3">
+        <v>1.7888543819998317</v>
+      </c>
+      <c r="G3">
+        <v>12.3</v>
+      </c>
+      <c r="H3">
+        <v>2.4135036772294316</v>
+      </c>
+      <c r="I3">
+        <v>33</v>
+      </c>
+      <c r="J3">
+        <v>2.318404623873926</v>
+      </c>
+      <c r="K3">
+        <v>22.666666666666664</v>
+      </c>
+      <c r="L3">
+        <v>1.2304019216861168</v>
+      </c>
+      <c r="M3">
+        <v>10.366666666666665</v>
+      </c>
+      <c r="N3">
+        <v>2.1711492092642786</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>2.8284271247461903</v>
+      </c>
+      <c r="G4">
+        <v>17.25</v>
+      </c>
+      <c r="H4">
+        <v>3.1819805153394638</v>
+      </c>
+      <c r="I4">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="K4">
+        <v>22.416666666666664</v>
+      </c>
+      <c r="L4">
+        <v>0.11785113019775875</v>
+      </c>
+      <c r="M4">
+        <v>5.9166666666666661</v>
+      </c>
+      <c r="N4">
+        <v>2.2391714737574029</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -518,7 +581,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66F790C-5674-4FFE-AFAC-55716215CEA8}">
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.3">
@@ -573,190 +636,695 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q3" t="e">
+      <c r="B3">
+        <v>81</v>
+      </c>
+      <c r="C3">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3">
+        <v>70</v>
+      </c>
+      <c r="G3">
+        <v>82</v>
+      </c>
+      <c r="H3">
+        <v>18</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>91</v>
+      </c>
+      <c r="L3">
+        <v>67</v>
+      </c>
+      <c r="M3">
+        <v>33</v>
+      </c>
+      <c r="N3">
+        <v>45</v>
+      </c>
+      <c r="O3">
+        <v>55</v>
+      </c>
+      <c r="Q3">
         <f>AVERAGE(C3:D3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R3" t="e">
+        <v>24.5</v>
+      </c>
+      <c r="R3">
         <f>AVERAGE(H3:I3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S3" t="e">
+        <v>13.5</v>
+      </c>
+      <c r="S3">
         <f>AVERAGE(M3:N3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T3" t="e">
+        <v>39</v>
+      </c>
+      <c r="T3">
         <f>AVERAGE(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U3" t="e">
+        <v>25.666666666666668</v>
+      </c>
+      <c r="U3">
         <f>MIN(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V3" t="e">
-        <f>(1/3)*(T3-U3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X3" t="e">
-        <f>AVERAGE(Q3)</f>
-        <v>#DIV/0!</v>
+        <v>13.5</v>
+      </c>
+      <c r="V3">
+        <f>T3-U3</f>
+        <v>12.166666666666668</v>
+      </c>
+      <c r="X3">
+        <f>AVERAGE(Q3:Q7)</f>
+        <v>23.5</v>
       </c>
       <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="e">
-        <f>AVERAGE(R3)</f>
-        <v>#DIV/0!</v>
+        <f>_xlfn.STDEV.S(Q3:Q7)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="Z3">
+        <f>AVERAGE(R3:R7)</f>
+        <v>13.6</v>
       </c>
       <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="e">
-        <f>AVERAGE(T3)</f>
-        <v>#DIV/0!</v>
+        <f>_xlfn.STDEV.S(R3:R7)</f>
+        <v>0.96176920308356728</v>
+      </c>
+      <c r="AB3">
+        <f>AVERAGE(S3:S7)</f>
+        <v>32.799999999999997</v>
       </c>
       <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="e">
-        <f>AVERAGE(T3)</f>
-        <v>#DIV/0!</v>
+        <f>_xlfn.STDEV.S(S3:S7)</f>
+        <v>4.1321907022788826</v>
+      </c>
+      <c r="AD3">
+        <f>AVERAGE(T3:T7)</f>
+        <v>23.3</v>
       </c>
       <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="e">
-        <f>AVERAGE(V3)</f>
-        <v>#DIV/0!</v>
+        <f>_xlfn.STDEV.S(T3:T7)</f>
+        <v>1.638935969191937</v>
+      </c>
+      <c r="AF3">
+        <f>AVERAGE(V3:V7)</f>
+        <v>9.6999999999999993</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <f>_xlfn.STDEV.S(V3:V7)</f>
+        <v>1.5872757934412172</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>18</v>
+      <c r="B4">
+        <v>79</v>
+      </c>
+      <c r="C4">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>25</v>
+      </c>
+      <c r="E4">
+        <v>75</v>
+      </c>
+      <c r="G4">
+        <v>80</v>
+      </c>
+      <c r="H4">
+        <v>20</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>92</v>
+      </c>
+      <c r="L4">
+        <v>74</v>
+      </c>
+      <c r="M4">
+        <v>26</v>
+      </c>
+      <c r="N4">
+        <v>34</v>
+      </c>
+      <c r="O4">
+        <v>66</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q14" si="0">AVERAGE(C4:D4)</f>
+        <v>23</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R14" si="1">AVERAGE(H4:I4)</f>
+        <v>14</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:S14" si="2">AVERAGE(M4:N4)</f>
+        <v>30</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T14" si="3">AVERAGE(Q4:S4)</f>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="U4">
+        <f t="shared" ref="U4:U14" si="4">MIN(Q4:S4)</f>
+        <v>14</v>
+      </c>
+      <c r="V4">
+        <f t="shared" ref="V4:V14" si="5">T4-U4</f>
+        <v>8.3333333333333321</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q5" t="e">
-        <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C5:D5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R5" t="e">
-        <f t="shared" ref="R5:R10" si="1">AVERAGE(H5:I5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S5" t="e">
-        <f t="shared" ref="S5:S10" si="2">AVERAGE(M5:N5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T5" t="e">
-        <f t="shared" ref="T5:T10" si="3">AVERAGE(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U5" t="e">
-        <f t="shared" ref="U5:U10" si="4">MIN(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V5" t="e">
-        <f t="shared" ref="V5:V10" si="5">(1/3)*(T5-U5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD5" t="e">
-        <f>AVERAGE(T5:T6)</f>
-        <v>#DIV/0!</v>
+      <c r="B5">
+        <v>85</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>31</v>
+      </c>
+      <c r="E5">
+        <v>69</v>
+      </c>
+      <c r="G5">
+        <v>80</v>
+      </c>
+      <c r="H5">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>90</v>
+      </c>
+      <c r="L5">
+        <v>66</v>
+      </c>
+      <c r="M5">
+        <v>34</v>
+      </c>
+      <c r="N5">
+        <v>35</v>
+      </c>
+      <c r="O5">
+        <v>65</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>34.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>24.166666666666668</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>9.1666666666666679</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q6" t="e">
+      <c r="B6">
+        <v>79</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>75</v>
+      </c>
+      <c r="G6">
+        <v>79</v>
+      </c>
+      <c r="H6">
+        <v>21</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>95</v>
+      </c>
+      <c r="L6">
+        <v>79</v>
+      </c>
+      <c r="M6">
+        <v>21</v>
+      </c>
+      <c r="N6">
+        <v>36</v>
+      </c>
+      <c r="O6">
+        <v>64</v>
+      </c>
+      <c r="Q6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R6" t="e">
+        <v>23</v>
+      </c>
+      <c r="R6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S6" t="e">
+        <v>13</v>
+      </c>
+      <c r="S6">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T6" t="e">
+        <v>28.5</v>
+      </c>
+      <c r="T6">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U6" t="e">
+        <v>21.5</v>
+      </c>
+      <c r="U6">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V6" t="e">
+        <v>13</v>
+      </c>
+      <c r="V6">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>84</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>68</v>
+      </c>
+      <c r="G7">
+        <v>88</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>87</v>
+      </c>
+      <c r="L7">
+        <v>68</v>
+      </c>
+      <c r="M7">
+        <v>32</v>
+      </c>
+      <c r="N7">
+        <v>32</v>
+      </c>
+      <c r="O7">
+        <v>68</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>22.833333333333332</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>12.5</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>10.333333333333332</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q9" t="e">
+      <c r="B9">
+        <v>84</v>
+      </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>26</v>
+      </c>
+      <c r="E9">
+        <v>74</v>
+      </c>
+      <c r="G9">
+        <v>75</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9">
+        <v>92</v>
+      </c>
+      <c r="L9">
+        <v>73</v>
+      </c>
+      <c r="M9">
+        <v>27</v>
+      </c>
+      <c r="N9">
+        <v>42</v>
+      </c>
+      <c r="O9">
+        <v>58</v>
+      </c>
+      <c r="Q9">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R9" t="e">
+        <v>21</v>
+      </c>
+      <c r="R9">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S9" t="e">
+        <v>16.5</v>
+      </c>
+      <c r="S9">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T9" t="e">
+        <v>34.5</v>
+      </c>
+      <c r="T9">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U9" t="e">
+        <v>24</v>
+      </c>
+      <c r="U9">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V9" t="e">
+        <v>16.5</v>
+      </c>
+      <c r="V9">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD9" t="e">
+        <v>7.5</v>
+      </c>
+      <c r="X9">
+        <f>AVERAGE(Q9:Q10)</f>
+        <v>21.75</v>
+      </c>
+      <c r="Y9">
+        <f>_xlfn.STDEV.S(Q9:Q10)</f>
+        <v>1.0606601717798212</v>
+      </c>
+      <c r="Z9">
+        <f>AVERAGE(R9:R10)</f>
+        <v>14.75</v>
+      </c>
+      <c r="AA9">
+        <f>_xlfn.STDEV.S(R9:R10)</f>
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="AB9">
+        <f>AVERAGE(S9:S10)</f>
+        <v>35</v>
+      </c>
+      <c r="AC9">
+        <f>_xlfn.STDEV.S(S9:S10)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="AD9">
         <f>AVERAGE(T9:T10)</f>
-        <v>#DIV/0!</v>
+        <v>23.833333333333336</v>
+      </c>
+      <c r="AE9">
+        <f>_xlfn.STDEV.S(T9:T10)</f>
+        <v>0.23570226039551501</v>
+      </c>
+      <c r="AF9">
+        <f>AVERAGE(V9:V10)</f>
+        <v>9.0833333333333339</v>
+      </c>
+      <c r="AG9">
+        <f>_xlfn.STDEV.S(V9:V10)</f>
+        <v>2.2391714737573998</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q10" t="e">
+      <c r="B10">
+        <v>85</v>
+      </c>
+      <c r="C10">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>70</v>
+      </c>
+      <c r="G10">
+        <v>82</v>
+      </c>
+      <c r="H10">
+        <v>18</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+      <c r="J10">
+        <v>92</v>
+      </c>
+      <c r="L10">
+        <v>76</v>
+      </c>
+      <c r="M10">
+        <v>24</v>
+      </c>
+      <c r="N10">
+        <v>47</v>
+      </c>
+      <c r="O10">
+        <v>53</v>
+      </c>
+      <c r="Q10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R10" t="e">
+        <v>22.5</v>
+      </c>
+      <c r="R10">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S10" t="e">
+        <v>13</v>
+      </c>
+      <c r="S10">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T10" t="e">
+        <v>35.5</v>
+      </c>
+      <c r="T10">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U10" t="e">
+        <v>23.666666666666668</v>
+      </c>
+      <c r="U10">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V10" t="e">
+        <v>13</v>
+      </c>
+      <c r="V10">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>10.666666666666668</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>82</v>
+      </c>
+      <c r="C13">
+        <v>18</v>
+      </c>
+      <c r="D13">
+        <v>26</v>
+      </c>
+      <c r="E13">
+        <v>74</v>
+      </c>
+      <c r="G13">
+        <v>75</v>
+      </c>
+      <c r="H13">
+        <v>25</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <v>95</v>
+      </c>
+      <c r="L13">
+        <v>78</v>
+      </c>
+      <c r="M13">
+        <v>22</v>
+      </c>
+      <c r="N13">
+        <v>39</v>
+      </c>
+      <c r="O13">
+        <v>61</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="2"/>
+        <v>30.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="3"/>
+        <v>22.5</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="5"/>
+        <v>7.5</v>
+      </c>
+      <c r="X13">
+        <f>AVERAGE(Q13:Q14)</f>
+        <v>20</v>
+      </c>
+      <c r="Y13">
+        <f>_xlfn.STDEV.S(Q13:Q14)</f>
+        <v>2.8284271247461903</v>
+      </c>
+      <c r="Z13">
+        <f>AVERAGE(R13:R14)</f>
+        <v>17.25</v>
+      </c>
+      <c r="AA13">
+        <f>_xlfn.STDEV.S(R13:R14)</f>
+        <v>3.1819805153394638</v>
+      </c>
+      <c r="AB13">
+        <f>AVERAGE(S13:S14)</f>
+        <v>30</v>
+      </c>
+      <c r="AC13">
+        <f>_xlfn.STDEV.S(S13:S14)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="AD13">
+        <f>AVERAGE(T13:T14)</f>
+        <v>22.416666666666664</v>
+      </c>
+      <c r="AE13">
+        <f>_xlfn.STDEV.S(T13:T14)</f>
+        <v>0.11785113019775875</v>
+      </c>
+      <c r="AF13">
+        <f>AVERAGE(V13:V14)</f>
+        <v>5.9166666666666661</v>
+      </c>
+      <c r="AG13">
+        <f>_xlfn.STDEV.S(V13:V14)</f>
+        <v>2.2391714737574029</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>84</v>
+      </c>
+      <c r="C14">
+        <v>16</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>80</v>
+      </c>
+      <c r="G14">
+        <v>69</v>
+      </c>
+      <c r="H14">
+        <v>31</v>
+      </c>
+      <c r="I14">
+        <v>8</v>
+      </c>
+      <c r="J14">
+        <v>92</v>
+      </c>
+      <c r="L14">
+        <v>78</v>
+      </c>
+      <c r="M14">
+        <v>22</v>
+      </c>
+      <c r="N14">
+        <v>37</v>
+      </c>
+      <c r="O14">
+        <v>63</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="2"/>
+        <v>29.5</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="3"/>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="5"/>
+        <v>4.3333333333333321</v>
       </c>
     </row>
   </sheetData>
@@ -766,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07FDE21E-9CB3-45CD-ADE0-EE4270AB04E7}">
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.3">
@@ -821,203 +1389,695 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>23</v>
+      </c>
+      <c r="E3">
+        <v>77</v>
+      </c>
+      <c r="G3">
+        <v>84</v>
+      </c>
+      <c r="H3">
+        <v>16</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>92</v>
+      </c>
+      <c r="L3">
+        <v>72</v>
+      </c>
+      <c r="M3">
+        <v>28</v>
+      </c>
+      <c r="N3">
+        <v>36</v>
+      </c>
+      <c r="O3">
+        <v>64</v>
+      </c>
+      <c r="Q3">
+        <f>AVERAGE(C3:D3)</f>
+        <v>21.5</v>
+      </c>
+      <c r="R3">
+        <f>AVERAGE(H3:I3)</f>
+        <v>12</v>
+      </c>
+      <c r="S3">
+        <f>AVERAGE(M3:N3)</f>
+        <v>32</v>
+      </c>
+      <c r="T3">
+        <f>AVERAGE(Q3:S3)</f>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="U3">
+        <f>MIN(Q3:S3)</f>
+        <v>12</v>
+      </c>
+      <c r="V3">
+        <f>T3-U3</f>
+        <v>9.8333333333333321</v>
+      </c>
+      <c r="X3">
+        <f>AVERAGE(Q3:Q7)</f>
+        <v>22.7</v>
+      </c>
+      <c r="Y3">
+        <f>_xlfn.STDEV.S(Q3:Q7)</f>
+        <v>1.7888543819998317</v>
+      </c>
+      <c r="Z3">
+        <f>AVERAGE(R3:R7)</f>
+        <v>12.3</v>
+      </c>
+      <c r="AA3">
+        <f>_xlfn.STDEV.S(R3:R7)</f>
+        <v>2.4135036772294316</v>
+      </c>
+      <c r="AB3">
+        <f>AVERAGE(S3:S7)</f>
+        <v>33</v>
+      </c>
+      <c r="AC3">
+        <f>_xlfn.STDEV.S(S3:S7)</f>
+        <v>2.318404623873926</v>
+      </c>
+      <c r="AD3">
+        <f>AVERAGE(T3:T7)</f>
+        <v>22.666666666666664</v>
+      </c>
+      <c r="AE3">
+        <f>_xlfn.STDEV.S(T3:T7)</f>
+        <v>1.2304019216861168</v>
+      </c>
+      <c r="AF3">
+        <f>AVERAGE(V3:V7)</f>
+        <v>10.366666666666665</v>
+      </c>
+      <c r="AG3">
+        <f>_xlfn.STDEV.S(V3:V7)</f>
+        <v>2.1711492092642786</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>79</v>
+      </c>
+      <c r="C4">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>70</v>
+      </c>
+      <c r="G4">
+        <v>83</v>
+      </c>
+      <c r="H4">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q3" t="e">
-        <f>AVERAGE(C3:D3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R3" t="e">
-        <f>AVERAGE(H3:I3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S3" t="e">
-        <f>AVERAGE(M3:N3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T3" t="e">
-        <f>AVERAGE(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U3" t="e">
-        <f>MIN(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V3" t="e">
-        <f>(1/3)*(T3-U3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X3" t="e">
-        <f>AVERAGE(Q3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD3" t="e">
-        <f>AVERAGE(T3)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>98</v>
+      </c>
+      <c r="L4">
+        <v>73</v>
+      </c>
+      <c r="M4">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>44</v>
+      </c>
+      <c r="O4">
+        <v>56</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q14" si="0">AVERAGE(C4:D4)</f>
+        <v>25.5</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R14" si="1">AVERAGE(H4:I4)</f>
+        <v>9.5</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:S14" si="2">AVERAGE(M4:N4)</f>
+        <v>35.5</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T14" si="3">AVERAGE(Q4:S4)</f>
+        <v>23.5</v>
+      </c>
+      <c r="U4">
+        <f t="shared" ref="U4:U14" si="4">MIN(Q4:S4)</f>
+        <v>9.5</v>
+      </c>
+      <c r="V4">
+        <f t="shared" ref="V4:V14" si="5">T4-U4</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>81</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>24</v>
+      </c>
+      <c r="E5">
+        <v>76</v>
+      </c>
+      <c r="G5">
+        <v>87</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>92</v>
+      </c>
+      <c r="L5">
+        <v>79</v>
+      </c>
+      <c r="M5">
+        <v>21</v>
+      </c>
+      <c r="N5">
+        <v>41</v>
+      </c>
+      <c r="O5">
+        <v>59</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>21.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>10.5</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>83</v>
+      </c>
+      <c r="C6">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>70</v>
+      </c>
+      <c r="G6">
+        <v>82</v>
+      </c>
+      <c r="H6">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q5" t="e">
-        <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C5:D5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R5" t="e">
-        <f t="shared" ref="R5:R10" si="1">AVERAGE(H5:I5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S5" t="e">
-        <f t="shared" ref="S5:S10" si="2">AVERAGE(M5:N5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T5" t="e">
-        <f t="shared" ref="T5:T10" si="3">AVERAGE(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U5" t="e">
-        <f t="shared" ref="U5:U10" si="4">MIN(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V5" t="e">
-        <f t="shared" ref="V5:V10" si="5">(1/3)*(T5-U5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X5" t="e">
-        <f>AVERAGE(Q5:Q6)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD5" t="e">
-        <f>AVERAGE(T5:T6)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q6" t="e">
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>89</v>
+      </c>
+      <c r="L6">
+        <v>66</v>
+      </c>
+      <c r="M6">
+        <v>34</v>
+      </c>
+      <c r="N6">
+        <v>28</v>
+      </c>
+      <c r="O6">
+        <v>72</v>
+      </c>
+      <c r="Q6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R6" t="e">
+        <v>23.5</v>
+      </c>
+      <c r="R6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S6" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="S6">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T6" t="e">
+        <v>31</v>
+      </c>
+      <c r="T6">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U6" t="e">
+        <v>23</v>
+      </c>
+      <c r="U6">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V6" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="V6">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>90</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>33</v>
+      </c>
+      <c r="E7">
+        <v>67</v>
+      </c>
+      <c r="G7">
+        <v>77</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>93</v>
+      </c>
+      <c r="L7">
+        <v>66</v>
+      </c>
+      <c r="M7">
+        <v>34</v>
+      </c>
+      <c r="N7">
+        <v>37</v>
+      </c>
+      <c r="O7">
+        <v>63</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>21.5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>35.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>82</v>
+      </c>
+      <c r="C9">
+        <v>18</v>
+      </c>
+      <c r="D9">
+        <v>26</v>
+      </c>
+      <c r="E9">
+        <v>74</v>
+      </c>
+      <c r="G9">
+        <v>75</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9">
+        <v>93</v>
+      </c>
+      <c r="L9">
+        <v>70</v>
+      </c>
+      <c r="M9">
+        <v>30</v>
+      </c>
+      <c r="N9">
+        <v>45</v>
+      </c>
+      <c r="O9">
+        <v>55</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>37.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>25.166666666666668</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>9.1666666666666679</v>
+      </c>
+      <c r="X9">
+        <f>AVERAGE(Q9:Q10)</f>
+        <v>20.75</v>
+      </c>
+      <c r="Y9">
+        <f>_xlfn.STDEV.S(Q9:Q10)</f>
+        <v>1.7677669529663689</v>
+      </c>
+      <c r="Z9">
+        <f>AVERAGE(R9:R10)</f>
+        <v>14.75</v>
+      </c>
+      <c r="AA9">
+        <f>_xlfn.STDEV.S(R9:R10)</f>
+        <v>1.7677669529663689</v>
+      </c>
+      <c r="AB9">
+        <f>AVERAGE(S9:S10)</f>
+        <v>34.25</v>
+      </c>
+      <c r="AC9">
+        <f>_xlfn.STDEV.S(S9:S10)</f>
+        <v>4.5961940777125587</v>
+      </c>
+      <c r="AD9">
+        <f>AVERAGE(T9:T10)</f>
+        <v>23.25</v>
+      </c>
+      <c r="AE9">
+        <f>_xlfn.STDEV.S(T9:T10)</f>
+        <v>2.7105759945484338</v>
+      </c>
+      <c r="AF9">
+        <f>AVERAGE(V9:V10)</f>
+        <v>8.5</v>
+      </c>
+      <c r="AG9">
+        <f>_xlfn.STDEV.S(V9:V10)</f>
+        <v>0.94280904158206502</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>83</v>
+      </c>
+      <c r="C10">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>22</v>
+      </c>
+      <c r="E10">
+        <v>78</v>
+      </c>
+      <c r="G10">
+        <v>81</v>
+      </c>
+      <c r="H10">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q9" t="e">
+      <c r="I10">
+        <v>8</v>
+      </c>
+      <c r="J10">
+        <v>92</v>
+      </c>
+      <c r="L10">
+        <v>78</v>
+      </c>
+      <c r="M10">
+        <v>22</v>
+      </c>
+      <c r="N10">
+        <v>40</v>
+      </c>
+      <c r="O10">
+        <v>60</v>
+      </c>
+      <c r="Q10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R9" t="e">
+        <v>19.5</v>
+      </c>
+      <c r="R10">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S9" t="e">
+        <v>13.5</v>
+      </c>
+      <c r="S10">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T9" t="e">
+        <v>31</v>
+      </c>
+      <c r="T10">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U9" t="e">
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U10">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V9" t="e">
+        <v>13.5</v>
+      </c>
+      <c r="V10">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X9" t="e">
-        <f>AVERAGE(Q9:Q10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y9" t="e">
-        <f>_xlfn.STDEV.S(Q9:Q10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z9" t="e">
-        <f>AVERAGE(R9:R10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA9" t="e">
-        <f>_xlfn.STDEV.S(R9:R10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB9" t="e">
-        <f>AVERAGE(S9:S10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC9" t="e">
-        <f>_xlfn.STDEV.S(S9:S10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD9" t="e">
-        <f>AVERAGE(T9:T10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE9" t="e">
-        <f>_xlfn.STDEV.S(T9:T10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF9" t="e">
-        <f>AVERAGE(V9:V10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG9" t="e">
-        <f>_xlfn.STDEV.S(V9:V10)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="Q10" t="e">
+        <v>7.8333333333333321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>76</v>
+      </c>
+      <c r="C13">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>32</v>
+      </c>
+      <c r="E13">
+        <v>68</v>
+      </c>
+      <c r="G13">
+        <v>84</v>
+      </c>
+      <c r="H13">
+        <v>16</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <v>90</v>
+      </c>
+      <c r="L13">
+        <v>67</v>
+      </c>
+      <c r="M13">
+        <v>33</v>
+      </c>
+      <c r="N13">
+        <v>49</v>
+      </c>
+      <c r="O13">
+        <v>51</v>
+      </c>
+      <c r="Q13">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R10" t="e">
+        <v>28</v>
+      </c>
+      <c r="R13">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S10" t="e">
+        <v>13</v>
+      </c>
+      <c r="S13">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T10" t="e">
+        <v>41</v>
+      </c>
+      <c r="T13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U10" t="e">
+        <v>27.333333333333332</v>
+      </c>
+      <c r="U13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V10" t="e">
+        <v>13</v>
+      </c>
+      <c r="V13">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>14.333333333333332</v>
+      </c>
+      <c r="X13">
+        <f>AVERAGE(Q13:Q14)</f>
+        <v>24.75</v>
+      </c>
+      <c r="Y13">
+        <f>_xlfn.STDEV.S(Q13:Q14)</f>
+        <v>4.5961940777125587</v>
+      </c>
+      <c r="Z13">
+        <f>AVERAGE(R13:R14)</f>
+        <v>14.5</v>
+      </c>
+      <c r="AA13">
+        <f>_xlfn.STDEV.S(R13:R14)</f>
+        <v>2.1213203435596424</v>
+      </c>
+      <c r="AB13">
+        <f>AVERAGE(S13:S14)</f>
+        <v>40.75</v>
+      </c>
+      <c r="AC13">
+        <f>_xlfn.STDEV.S(S13:S14)</f>
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="AD13">
+        <f>AVERAGE(T13:T14)</f>
+        <v>26.666666666666664</v>
+      </c>
+      <c r="AE13">
+        <f>_xlfn.STDEV.S(T13:T14)</f>
+        <v>0.94280904158206247</v>
+      </c>
+      <c r="AF13">
+        <f>AVERAGE(V13:V14)</f>
+        <v>12.166666666666666</v>
+      </c>
+      <c r="AG13">
+        <f>_xlfn.STDEV.S(V13:V14)</f>
+        <v>3.0641293851417006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>81</v>
+      </c>
+      <c r="C14">
+        <v>19</v>
+      </c>
+      <c r="D14">
+        <v>24</v>
+      </c>
+      <c r="E14">
+        <v>76</v>
+      </c>
+      <c r="G14">
+        <v>82</v>
+      </c>
+      <c r="H14">
+        <v>18</v>
+      </c>
+      <c r="I14">
+        <v>14</v>
+      </c>
+      <c r="J14">
+        <v>86</v>
+      </c>
+      <c r="L14">
+        <v>65</v>
+      </c>
+      <c r="M14">
+        <v>35</v>
+      </c>
+      <c r="N14">
+        <v>46</v>
+      </c>
+      <c r="O14">
+        <v>54</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>21.5</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="2"/>
+        <v>40.5</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="5"/>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1027,10 +2087,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F52E050-0D53-43C0-B5FC-AD6D7416AA3A}">
-  <dimension ref="Q1:AG2"/>
+  <dimension ref="B1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="17:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:33" x14ac:dyDescent="0.3">
       <c r="Q1" t="s">
         <v>0</v>
       </c>
@@ -1080,63 +2140,668 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="17:33" x14ac:dyDescent="0.3">
-      <c r="Q2" t="e">
+    <row r="2" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>86</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>26</v>
+      </c>
+      <c r="E2">
+        <v>74</v>
+      </c>
+      <c r="G2">
+        <v>88</v>
+      </c>
+      <c r="H2">
+        <v>12</v>
+      </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <v>92</v>
+      </c>
+      <c r="L2">
+        <v>73</v>
+      </c>
+      <c r="M2">
+        <v>27</v>
+      </c>
+      <c r="N2">
+        <v>39</v>
+      </c>
+      <c r="O2">
+        <v>61</v>
+      </c>
+      <c r="Q2">
         <f>AVERAGE(C2:D2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R2" t="e">
+        <v>20</v>
+      </c>
+      <c r="R2">
         <f>AVERAGE(H2:I2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S2" t="e">
+        <v>10</v>
+      </c>
+      <c r="S2">
         <f>AVERAGE(M2:N2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T2" t="e">
+        <v>33</v>
+      </c>
+      <c r="T2">
         <f>AVERAGE(Q2:S2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U2" t="e">
+        <v>21</v>
+      </c>
+      <c r="U2">
         <f>MIN(Q2:S2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V2" t="e">
-        <f>(1/3)*(T2-U2)</f>
-        <v>#DIV/0!</v>
+        <v>10</v>
+      </c>
+      <c r="V2">
+        <f>T2-U2</f>
+        <v>11</v>
       </c>
       <c r="X2">
+        <f>AVERAGE(Q2:Q11)</f>
+        <v>21.65</v>
+      </c>
+      <c r="Y2">
+        <f>_xlfn.STDEV.S(Q2:Q11)</f>
+        <v>1.8112303982529543</v>
+      </c>
+      <c r="Z2">
+        <f>AVERAGE(R2:R11)</f>
+        <v>12.75</v>
+      </c>
+      <c r="AA2">
+        <f>_xlfn.STDEV.S(R2:R11)</f>
+        <v>2.3003622903070435</v>
+      </c>
+      <c r="AB2">
+        <f>AVERAGE(S2:S11)</f>
+        <v>31.05</v>
+      </c>
+      <c r="AC2">
+        <f>_xlfn.STDEV.S(S2:S11)</f>
+        <v>2.4318488622628025</v>
+      </c>
+      <c r="AD2">
+        <f>AVERAGE(T2:T11)</f>
+        <v>21.81666666666667</v>
+      </c>
+      <c r="AE2">
+        <f>_xlfn.STDEV.S(T2:T11)</f>
+        <v>0.86584719092036688</v>
+      </c>
+      <c r="AF2">
+        <f>AVERAGE(V2:V11)</f>
+        <v>9.0666666666666664</v>
+      </c>
+      <c r="AG2">
+        <f>_xlfn.STDEV.S(V2:V11)</f>
+        <v>1.6872799353536168</v>
+      </c>
+    </row>
+    <row r="3" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>78</v>
+      </c>
+      <c r="C3">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>23</v>
+      </c>
+      <c r="E3">
+        <v>77</v>
+      </c>
+      <c r="G3">
+        <v>82</v>
+      </c>
+      <c r="H3">
         <v>18</v>
       </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>19.5</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>29.5</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>91</v>
+      </c>
+      <c r="L3">
+        <v>70</v>
+      </c>
+      <c r="M3">
+        <v>30</v>
+      </c>
+      <c r="N3">
+        <v>26</v>
+      </c>
+      <c r="O3">
+        <v>74</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="0">AVERAGE(C3:D3)</f>
+        <v>22.5</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="1">AVERAGE(H3:I3)</f>
+        <v>13.5</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S11" si="2">AVERAGE(M3:N3)</f>
+        <v>28</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="3">AVERAGE(Q3:S3)</f>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="4">MIN(Q3:S3)</f>
+        <v>13.5</v>
+      </c>
+      <c r="V3">
+        <f t="shared" ref="V3:V11" si="5">T3-U3</f>
+        <v>7.8333333333333321</v>
+      </c>
+    </row>
+    <row r="4" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>82</v>
+      </c>
+      <c r="C4">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>70</v>
+      </c>
+      <c r="G4">
+        <v>81</v>
+      </c>
+      <c r="H4">
+        <v>19</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>92</v>
+      </c>
+      <c r="L4">
+        <v>72</v>
+      </c>
+      <c r="M4">
+        <v>28</v>
+      </c>
+      <c r="N4">
+        <v>34</v>
+      </c>
+      <c r="O4">
+        <v>66</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="1"/>
+        <v>13.5</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="3"/>
+        <v>22.833333333333332</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="4"/>
+        <v>13.5</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="5"/>
+        <v>9.3333333333333321</v>
+      </c>
+    </row>
+    <row r="5" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>76</v>
+      </c>
+      <c r="C5">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>22</v>
+      </c>
+      <c r="E5">
+        <v>78</v>
+      </c>
+      <c r="G5">
+        <v>85</v>
+      </c>
+      <c r="H5">
+        <v>15</v>
+      </c>
+      <c r="I5">
+        <v>15</v>
+      </c>
+      <c r="J5">
+        <v>85</v>
+      </c>
+      <c r="L5">
+        <v>78</v>
+      </c>
+      <c r="M5">
+        <v>22</v>
+      </c>
+      <c r="N5">
+        <v>33</v>
+      </c>
+      <c r="O5">
+        <v>67</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>27.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>6.8333333333333321</v>
+      </c>
+    </row>
+    <row r="6" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>80</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>77</v>
+      </c>
+      <c r="G6">
+        <v>84</v>
+      </c>
+      <c r="H6">
+        <v>16</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>93</v>
+      </c>
+      <c r="L6">
+        <v>63</v>
+      </c>
+      <c r="M6">
+        <v>37</v>
+      </c>
+      <c r="N6">
+        <v>24</v>
+      </c>
+      <c r="O6">
+        <v>76</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>21.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>30.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>11.5</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>9.6666666666666679</v>
+      </c>
+    </row>
+    <row r="7" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>86</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>29</v>
+      </c>
+      <c r="E7">
+        <v>71</v>
+      </c>
+      <c r="G7">
+        <v>86</v>
+      </c>
+      <c r="H7">
+        <v>14</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>90</v>
+      </c>
+      <c r="L7">
+        <v>72</v>
+      </c>
+      <c r="M7">
+        <v>28</v>
+      </c>
+      <c r="N7">
+        <v>39</v>
+      </c>
+      <c r="O7">
+        <v>61</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>21.5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>33.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
         <v>22.333333333333332</v>
       </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>1.444444444444444</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>10.333333333333332</v>
+      </c>
+    </row>
+    <row r="8" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>88</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>31</v>
+      </c>
+      <c r="E8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>84</v>
+      </c>
+      <c r="H8">
+        <v>16</v>
+      </c>
+      <c r="I8">
+        <v>8</v>
+      </c>
+      <c r="J8">
+        <v>92</v>
+      </c>
+      <c r="L8">
+        <v>68</v>
+      </c>
+      <c r="M8">
+        <v>32</v>
+      </c>
+      <c r="N8">
+        <v>29</v>
+      </c>
+      <c r="O8">
+        <v>71</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>21.5</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>30.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>9.3333333333333321</v>
+      </c>
+    </row>
+    <row r="9" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>84</v>
+      </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>29</v>
+      </c>
+      <c r="E9">
+        <v>71</v>
+      </c>
+      <c r="G9">
+        <v>77</v>
+      </c>
+      <c r="H9">
+        <v>23</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>90</v>
+      </c>
+      <c r="L9">
+        <v>68</v>
+      </c>
+      <c r="M9">
+        <v>32</v>
+      </c>
+      <c r="N9">
+        <v>30</v>
+      </c>
+      <c r="O9">
+        <v>70</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>22.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>23.333333333333332</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>16.5</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>6.8333333333333321</v>
+      </c>
+    </row>
+    <row r="10" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>84</v>
+      </c>
+      <c r="C10">
+        <v>16</v>
+      </c>
+      <c r="D10">
+        <v>19</v>
+      </c>
+      <c r="E10">
+        <v>81</v>
+      </c>
+      <c r="G10">
+        <v>91</v>
+      </c>
+      <c r="H10">
+        <v>9</v>
+      </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
+      <c r="J10">
+        <v>91</v>
+      </c>
+      <c r="L10">
+        <v>75</v>
+      </c>
+      <c r="M10">
+        <v>25</v>
+      </c>
+      <c r="N10">
+        <v>46</v>
+      </c>
+      <c r="O10">
+        <v>54</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>35.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>20.666666666666668</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="5"/>
+        <v>11.666666666666668</v>
+      </c>
+    </row>
+    <row r="11" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>85</v>
+      </c>
+      <c r="C11">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>30</v>
+      </c>
+      <c r="E11">
+        <v>70</v>
+      </c>
+      <c r="G11">
+        <v>83</v>
+      </c>
+      <c r="H11">
+        <v>17</v>
+      </c>
+      <c r="I11">
+        <v>12</v>
+      </c>
+      <c r="J11">
+        <v>88</v>
+      </c>
+      <c r="L11">
+        <v>74</v>
+      </c>
+      <c r="M11">
+        <v>26</v>
+      </c>
+      <c r="N11">
+        <v>34</v>
+      </c>
+      <c r="O11">
+        <v>66</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>22.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>14.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="5"/>
+        <v>7.8333333333333321</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DataAnalysis/CJ/0.2/Results.xlsx
+++ b/DataAnalysis/CJ/0.2/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CJ\0.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136CEC64-E386-448A-AC3D-5D8FB9C3CFA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC03043B-C409-4F73-A701-A0C7ACC65D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>ERR_i_0</t>
   </si>
@@ -105,12 +105,6 @@
   </si>
   <si>
     <t>ADV_NOCLSDIV</t>
-  </si>
-  <si>
-    <t>ep=0.1</t>
-  </si>
-  <si>
-    <t>ep=0.0001</t>
   </si>
 </sst>
 </file>
@@ -428,149 +422,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
+      <c r="B2">
+        <v>21.65</v>
+      </c>
+      <c r="C2">
+        <v>1.8112303982529543</v>
+      </c>
+      <c r="D2">
+        <v>12.75</v>
+      </c>
       <c r="E2">
-        <v>21.65</v>
+        <v>2.3003622903070435</v>
       </c>
       <c r="F2">
-        <v>1.8112303982529543</v>
+        <v>31.05</v>
       </c>
       <c r="G2">
-        <v>12.75</v>
+        <v>2.4318488622628025</v>
       </c>
       <c r="H2">
-        <v>2.3003622903070435</v>
+        <v>21.81666666666667</v>
       </c>
       <c r="I2">
-        <v>31.05</v>
+        <v>0.86584719092036688</v>
       </c>
       <c r="J2">
-        <v>2.4318488622628025</v>
+        <v>9.0666666666666664</v>
       </c>
       <c r="K2">
-        <v>21.81666666666667</v>
-      </c>
-      <c r="L2">
-        <v>0.86584719092036688</v>
-      </c>
-      <c r="M2">
-        <v>9.0666666666666664</v>
-      </c>
-      <c r="N2">
         <v>1.6872799353536168</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
-        <v>23</v>
+      <c r="B3">
+        <v>22.7</v>
+      </c>
+      <c r="C3">
+        <v>1.7888543819998317</v>
+      </c>
+      <c r="D3">
+        <v>12.3</v>
       </c>
       <c r="E3">
-        <v>22.7</v>
+        <v>2.4135036772294316</v>
       </c>
       <c r="F3">
-        <v>1.7888543819998317</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>12.3</v>
+        <v>2.318404623873926</v>
       </c>
       <c r="H3">
-        <v>2.4135036772294316</v>
+        <v>22.666666666666664</v>
       </c>
       <c r="I3">
-        <v>33</v>
+        <v>1.2304019216861168</v>
       </c>
       <c r="J3">
-        <v>2.318404623873926</v>
+        <v>10.366666666666665</v>
       </c>
       <c r="K3">
-        <v>22.666666666666664</v>
-      </c>
-      <c r="L3">
-        <v>1.2304019216861168</v>
-      </c>
-      <c r="M3">
-        <v>10.366666666666665</v>
-      </c>
-      <c r="N3">
         <v>2.1711492092642786</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
-        <v>22</v>
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>2.8284271247461903</v>
+      </c>
+      <c r="D4">
+        <v>17.25</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>3.1819805153394638</v>
       </c>
       <c r="F4">
-        <v>2.8284271247461903</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>17.25</v>
+        <v>0.70710678118654757</v>
       </c>
       <c r="H4">
-        <v>3.1819805153394638</v>
+        <v>22.416666666666664</v>
       </c>
       <c r="I4">
-        <v>30</v>
+        <v>0.11785113019775875</v>
       </c>
       <c r="J4">
-        <v>0.70710678118654757</v>
+        <v>5.9166666666666661</v>
       </c>
       <c r="K4">
-        <v>22.416666666666664</v>
-      </c>
-      <c r="L4">
-        <v>0.11785113019775875</v>
-      </c>
-      <c r="M4">
-        <v>5.9166666666666661</v>
-      </c>
-      <c r="N4">
         <v>2.2391714737574029</v>
       </c>
     </row>
